--- a/platform/public_facilities_gas.xlsx
+++ b/platform/public_facilities_gas.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -41,8 +41,12 @@
       <b val="1"/>
       <color rgb="009A5300"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +67,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B6B6"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +104,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -130,6 +139,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1080,55 +1099,63 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>구민회관</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="14" t="n">
         <v>228</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>노원구민의전당 사무동</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 중계동 1229 </t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n">
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="n">
         <v>4009</v>
       </c>
-      <c r="K8" s="1" t="inlineStr">
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O8" s="16" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
           <t>09:00~18:00</t>
@@ -1141,54 +1168,61 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>노원구시설관리</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="14" t="n">
         <v>17</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>월계문화체육센터</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 월계동 566-5 외9필지 </t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="14" t="n">
         <v>7999.52</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="K9" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="14" t="inlineStr">
         <is>
           <t>운동시설</t>
         </is>
       </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="n"/>
       <c r="P9" s="2" t="n"/>
       <c r="BH9" s="3" t="inlineStr">
         <is>
@@ -1579,55 +1613,63 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="14" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>보육지원과</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="14" t="n">
         <v>51</v>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>공릉2동어린이집</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 공릉동 758-6 </t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="n">
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="n">
         <v>3748.75</v>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="K15" s="16" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="14" t="inlineStr">
         <is>
           <t>어린이집</t>
         </is>
       </c>
+      <c r="N15" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="n"/>
       <c r="P15" s="2" t="n"/>
       <c r="BH15" s="3" t="inlineStr">
         <is>
@@ -1715,51 +1757,59 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>보육지원과</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>공릉2동어린이집</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 공릉동 77 </t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 공릉로42길 49 (공릉동)</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="3" t="n">
+      <c r="I17" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="14" t="n">
         <v>1559.57</v>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="K17" s="16" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="14" t="inlineStr">
         <is>
           <t>어린이집</t>
         </is>
       </c>
+      <c r="N17" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O17" s="16" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
           <t>06:00~22:00(월~금)/09:00~18:00(토)</t>
@@ -2429,54 +2479,61 @@
       <c r="BH25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>보육지원과</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="14" t="n">
         <v>173</v>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>수락한옥어린이집</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 118-4 </t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="n">
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="3" t="n">
+      <c r="I26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="14" t="n">
         <v>546.16</v>
       </c>
-      <c r="K26" s="1" t="n">
+      <c r="K26" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="14" t="inlineStr">
         <is>
           <t>08-교육연구 및 복지시설</t>
         </is>
       </c>
+      <c r="N26" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
           <t>06:00~22:00</t>
@@ -5266,53 +5323,61 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="14" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>자원순환</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n">
+      <c r="C64" s="14" t="n">
         <v>194</v>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>재활용센타(2관)</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 중계동 210-7 </t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 덕릉로 639 (중계동)</t>
         </is>
       </c>
-      <c r="H64" s="3" t="n">
+      <c r="H64" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="n">
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="n">
         <v>569.12</v>
       </c>
-      <c r="M64" s="3" t="inlineStr">
+      <c r="K64" s="16" t="n"/>
+      <c r="L64" s="16" t="n"/>
+      <c r="M64" s="14" t="inlineStr">
         <is>
           <t>03-제1종 근린생활시설</t>
         </is>
       </c>
+      <c r="N64" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O64" s="16" t="n"/>
       <c r="P64" s="2" t="n"/>
       <c r="BH64" s="3" t="inlineStr">
         <is>
@@ -5826,56 +5891,63 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="14" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>평생교육과</t>
         </is>
       </c>
-      <c r="C72" s="3" t="n">
+      <c r="C72" s="14" t="n">
         <v>132</v>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="14" t="inlineStr">
         <is>
           <t>노원평생교육원</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="14" t="inlineStr">
         <is>
           <t>01-공용재산</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F72" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 735 외1(노원평생교육원) </t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="G72" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 동일로217길 48 (상계동 외1(노원평생교육원))</t>
         </is>
       </c>
-      <c r="H72" s="3" t="n">
+      <c r="H72" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="I72" s="3" t="n">
+      <c r="I72" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="J72" s="3" t="n">
+      <c r="J72" s="14" t="n">
         <v>2321.9</v>
       </c>
-      <c r="K72" s="1" t="inlineStr">
+      <c r="K72" s="15" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M72" s="3" t="inlineStr">
+      <c r="L72" s="16" t="n"/>
+      <c r="M72" s="14" t="inlineStr">
         <is>
           <t>08-교육연구 및 복지시설</t>
         </is>
       </c>
+      <c r="N72" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O72" s="16" t="n"/>
       <c r="P72" s="2" t="inlineStr">
         <is>
           <t>09:00~18:00</t>
@@ -6403,25 +6475,39 @@
       <c r="BH79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="C80" s="3" t="n">
+      <c r="A80" s="16" t="n"/>
+      <c r="B80" s="16" t="n"/>
+      <c r="C80" s="14" t="n">
         <v>237</v>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="14" t="inlineStr">
         <is>
           <t>서울노원경찰서</t>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr">
+      <c r="E80" s="16" t="n"/>
+      <c r="F80" s="16" t="n"/>
+      <c r="G80" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울시 노원구 노원로 283 (하계동) </t>
         </is>
       </c>
-      <c r="H80" s="3" t="n">
+      <c r="H80" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="I80" s="16" t="n"/>
+      <c r="J80" s="14" t="n">
         <v>13333.21</v>
       </c>
+      <c r="K80" s="16" t="n"/>
+      <c r="L80" s="16" t="n"/>
+      <c r="M80" s="16" t="n"/>
+      <c r="N80" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O80" s="16" t="n"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
           <t>09:00~18:00</t>
@@ -6439,43 +6525,53 @@
       </c>
     </row>
     <row r="81">
-      <c r="C81" s="3" t="n">
+      <c r="A81" s="16" t="n"/>
+      <c r="B81" s="16" t="n"/>
+      <c r="C81" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="14" t="inlineStr">
         <is>
           <t>공릉동 행복주택</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E81" s="14" t="inlineStr">
         <is>
           <t>01-공용재산</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F81" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 공릉동 428-7 </t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="n">
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="I81" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="3" t="n">
+      <c r="I81" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="14" t="n">
         <v>6045.31</v>
       </c>
-      <c r="M81" s="3" t="inlineStr">
+      <c r="K81" s="16" t="n"/>
+      <c r="L81" s="16" t="n"/>
+      <c r="M81" s="14" t="inlineStr">
         <is>
           <t>공동주택</t>
         </is>
       </c>
+      <c r="N81" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O81" s="16" t="n"/>
       <c r="P81" s="2" t="n"/>
       <c r="BH81" s="3" t="inlineStr">
         <is>
@@ -7274,25 +7370,39 @@
       <c r="BH93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="C94" s="3" t="n">
+      <c r="A94" s="16" t="n"/>
+      <c r="B94" s="16" t="n"/>
+      <c r="C94" s="14" t="n">
         <v>236</v>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="14" t="inlineStr">
         <is>
           <t>노원이지센터</t>
         </is>
       </c>
-      <c r="H94" s="3" t="n">
+      <c r="E94" s="16" t="n"/>
+      <c r="F94" s="16" t="n"/>
+      <c r="G94" s="16" t="n"/>
+      <c r="H94" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="J94" s="3" t="n">
+      <c r="I94" s="16" t="n"/>
+      <c r="J94" s="14" t="n">
         <v>471.29</v>
       </c>
-      <c r="M94" s="3" t="inlineStr">
+      <c r="K94" s="16" t="n"/>
+      <c r="L94" s="16" t="n"/>
+      <c r="M94" s="14" t="inlineStr">
         <is>
           <t>홍보관</t>
         </is>
       </c>
+      <c r="N94" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O94" s="16" t="n"/>
       <c r="P94" s="2" t="n"/>
       <c r="BH94" s="3" t="inlineStr">
         <is>
@@ -8420,43 +8530,53 @@
       </c>
     </row>
     <row r="113">
-      <c r="C113" s="3" t="n">
+      <c r="A113" s="16" t="n"/>
+      <c r="B113" s="16" t="n"/>
+      <c r="C113" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D113" s="14" t="inlineStr">
         <is>
           <t>합동마을복지관(지하경로당 123층어린이집)</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="E113" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 111-158 </t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
+      <c r="G113" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 상계로33길 33 (상계동)</t>
         </is>
       </c>
-      <c r="H113" s="3" t="n">
+      <c r="H113" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="I113" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="3" t="n">
+      <c r="I113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="14" t="n">
         <v>318.32</v>
       </c>
-      <c r="M113" s="3" t="inlineStr">
+      <c r="K113" s="16" t="n"/>
+      <c r="L113" s="16" t="n"/>
+      <c r="M113" s="14" t="inlineStr">
         <is>
           <t>복지관</t>
         </is>
       </c>
+      <c r="N113" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O113" s="16" t="n"/>
       <c r="P113" s="2" t="n"/>
       <c r="BH113" s="3" t="inlineStr">
         <is>
@@ -8657,45 +8777,55 @@
       </c>
     </row>
     <row r="117">
-      <c r="C117" s="3" t="n">
+      <c r="A117" s="16" t="n"/>
+      <c r="B117" s="16" t="n"/>
+      <c r="C117" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D117" s="14" t="inlineStr">
         <is>
           <t>초안산 도자기체험장</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="E117" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F117" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 월계동 산 17-7 </t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
+      <c r="G117" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 덕릉로60타길 23  초안산도자기체험장 (월계동)</t>
         </is>
       </c>
-      <c r="H117" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J117" s="3" t="n">
+      <c r="H117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J117" s="14" t="n">
         <v>278.88</v>
       </c>
-      <c r="M117" s="3" t="inlineStr">
+      <c r="K117" s="16" t="n"/>
+      <c r="L117" s="16" t="n"/>
+      <c r="M117" s="14" t="inlineStr">
         <is>
           <t>관광휴게시설(도자기체험)</t>
         </is>
       </c>
+      <c r="N117" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O117" s="16" t="n"/>
       <c r="P117" s="2" t="n"/>
       <c r="BH117" s="3" t="inlineStr">
         <is>
@@ -9173,45 +9303,55 @@
       </c>
     </row>
     <row r="125">
-      <c r="C125" s="3" t="n">
+      <c r="A125" s="16" t="n"/>
+      <c r="B125" s="16" t="n"/>
+      <c r="C125" s="14" t="n">
         <v>232</v>
       </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D125" s="14" t="inlineStr">
         <is>
           <t>불암산생태학습관</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
+      <c r="E125" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 중계동 산 40-1 </t>
         </is>
       </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J125" s="3" t="n">
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J125" s="14" t="n">
         <v>224.19</v>
       </c>
-      <c r="M125" s="3" t="inlineStr">
+      <c r="K125" s="16" t="n"/>
+      <c r="L125" s="16" t="n"/>
+      <c r="M125" s="14" t="inlineStr">
         <is>
           <t>공원</t>
         </is>
       </c>
+      <c r="N125" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O125" s="16" t="n"/>
       <c r="P125" s="2" t="n"/>
       <c r="BH125" s="3" t="inlineStr">
         <is>
@@ -9697,43 +9837,53 @@
       </c>
     </row>
     <row r="133">
-      <c r="C133" s="3" t="n">
+      <c r="A133" s="16" t="n"/>
+      <c r="B133" s="16" t="n"/>
+      <c r="C133" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D133" s="14" t="inlineStr">
         <is>
           <t>불암산 목예공방</t>
         </is>
       </c>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="E133" s="14" t="inlineStr">
         <is>
           <t>01-공용재산</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
+      <c r="F133" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 하계동 9-5 </t>
         </is>
       </c>
-      <c r="G133" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H133" s="3" t="n">
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H133" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="I133" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J133" s="3" t="n">
+      <c r="I133" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" s="14" t="n">
         <v>196.08</v>
       </c>
-      <c r="M133" s="3" t="inlineStr">
+      <c r="K133" s="16" t="n"/>
+      <c r="L133" s="16" t="n"/>
+      <c r="M133" s="14" t="inlineStr">
         <is>
           <t>목공예체험장</t>
         </is>
       </c>
+      <c r="N133" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O133" s="16" t="n"/>
       <c r="P133" s="2" t="n"/>
       <c r="BH133" s="3" t="inlineStr">
         <is>
@@ -9809,22 +9959,37 @@
       <c r="BH134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="C135" s="3" t="n">
+      <c r="A135" s="16" t="n"/>
+      <c r="B135" s="16" t="n"/>
+      <c r="C135" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="D135" s="14" t="inlineStr">
         <is>
           <t>노원숲속의집</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr">
+      <c r="E135" s="16" t="n"/>
+      <c r="F135" s="16" t="n"/>
+      <c r="G135" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 월계로 44가길 78</t>
         </is>
       </c>
-      <c r="J135" s="3" t="n">
+      <c r="H135" s="16" t="n"/>
+      <c r="I135" s="16" t="n"/>
+      <c r="J135" s="14" t="n">
         <v>190</v>
       </c>
+      <c r="K135" s="16" t="n"/>
+      <c r="L135" s="16" t="n"/>
+      <c r="M135" s="16" t="n"/>
+      <c r="N135" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O135" s="16" t="n"/>
       <c r="P135" s="2" t="inlineStr">
         <is>
           <t>10:00~17:00</t>
@@ -10033,47 +10198,57 @@
       </c>
     </row>
     <row r="139">
-      <c r="C139" s="3" t="n">
+      <c r="A139" s="16" t="n"/>
+      <c r="B139" s="16" t="n"/>
+      <c r="C139" s="14" t="n">
         <v>189</v>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="D139" s="14" t="inlineStr">
         <is>
           <t>학대피해아동쉼터</t>
         </is>
       </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="E139" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F139" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 중계동 90-30 </t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J139" s="3" t="n">
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H139" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J139" s="14" t="n">
         <v>143.66</v>
       </c>
-      <c r="M139" s="3" t="inlineStr">
+      <c r="K139" s="16" t="n"/>
+      <c r="L139" s="16" t="n"/>
+      <c r="M139" s="14" t="inlineStr">
         <is>
           <t>02-공동주택</t>
         </is>
       </c>
+      <c r="N139" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O139" s="16" t="n"/>
       <c r="P139" s="2" t="inlineStr">
         <is>
           <t>10:00~17:00</t>
@@ -10397,43 +10572,53 @@
       <c r="BH143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="C144" s="3" t="n">
+      <c r="A144" s="16" t="n"/>
+      <c r="B144" s="16" t="n"/>
+      <c r="C144" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="D144" s="14" t="inlineStr">
         <is>
           <t>구립한마음경로당</t>
         </is>
       </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F144" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 공릉동 584-19 </t>
         </is>
       </c>
-      <c r="G144" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="n">
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="I144" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J144" s="3" t="n">
+      <c r="I144" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J144" s="14" t="n">
         <v>134.81</v>
       </c>
-      <c r="M144" s="3" t="inlineStr">
+      <c r="K144" s="16" t="n"/>
+      <c r="L144" s="16" t="n"/>
+      <c r="M144" s="14" t="inlineStr">
         <is>
           <t>경로당</t>
         </is>
       </c>
+      <c r="N144" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O144" s="16" t="n"/>
       <c r="P144" s="2" t="inlineStr">
         <is>
           <t>09:00~21:00(화~토)/09:00~18:00(일)</t>
@@ -10527,45 +10712,55 @@
       <c r="BH145" s="3" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="C146" s="3" t="n">
+      <c r="A146" s="16" t="n"/>
+      <c r="B146" s="16" t="n"/>
+      <c r="C146" s="14" t="n">
         <v>82</v>
       </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="D146" s="14" t="inlineStr">
         <is>
           <t>송암경로당</t>
         </is>
       </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
+      <c r="E146" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F146" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 138-63 </t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr">
+      <c r="G146" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 한글비석로44길 64-20 (상계동)</t>
         </is>
       </c>
-      <c r="H146" s="3" t="n">
+      <c r="H146" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J146" s="3" t="n">
+      <c r="I146" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J146" s="14" t="n">
         <v>134.11</v>
       </c>
-      <c r="M146" s="3" t="inlineStr">
+      <c r="K146" s="16" t="n"/>
+      <c r="L146" s="16" t="n"/>
+      <c r="M146" s="14" t="inlineStr">
         <is>
           <t>경로당</t>
         </is>
       </c>
+      <c r="N146" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O146" s="16" t="n"/>
       <c r="P146" s="2" t="inlineStr">
         <is>
           <t>09:00~18:00</t>
@@ -10715,43 +10910,53 @@
       </c>
     </row>
     <row r="149">
-      <c r="C149" s="3" t="n">
+      <c r="A149" s="16" t="n"/>
+      <c r="B149" s="16" t="n"/>
+      <c r="C149" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D149" s="14" t="inlineStr">
         <is>
           <t>벼루마을경로당</t>
         </is>
       </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
+      <c r="E149" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F149" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 월계동 534-156 </t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr">
+      <c r="G149" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 월계로44길 62 (월계동)</t>
         </is>
       </c>
-      <c r="H149" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I149" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J149" s="3" t="n">
+      <c r="H149" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="14" t="n">
         <v>125.26</v>
       </c>
-      <c r="M149" s="3" t="inlineStr">
+      <c r="K149" s="16" t="n"/>
+      <c r="L149" s="16" t="n"/>
+      <c r="M149" s="14" t="inlineStr">
         <is>
           <t>경로당</t>
         </is>
       </c>
+      <c r="N149" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O149" s="16" t="n"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
           <t>09:00~18:00</t>
@@ -11385,45 +11590,55 @@
       <c r="BH158" s="3" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="C159" s="3" t="n">
+      <c r="A159" s="16" t="n"/>
+      <c r="B159" s="16" t="n"/>
+      <c r="C159" s="14" t="n">
         <v>193</v>
       </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="D159" s="14" t="inlineStr">
         <is>
           <t>한우리경로당</t>
         </is>
       </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F159" s="3" t="inlineStr">
+      <c r="E159" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F159" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 중계동 133-27 </t>
         </is>
       </c>
-      <c r="G159" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H159" s="3" t="n">
+      <c r="G159" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H159" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="I159" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J159" s="3" t="n">
+      <c r="I159" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J159" s="14" t="n">
         <v>98.72</v>
       </c>
-      <c r="M159" s="3" t="inlineStr">
+      <c r="K159" s="16" t="n"/>
+      <c r="L159" s="16" t="n"/>
+      <c r="M159" s="14" t="inlineStr">
         <is>
           <t>01-단독주택</t>
         </is>
       </c>
+      <c r="N159" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O159" s="16" t="n"/>
       <c r="P159" s="2" t="inlineStr">
         <is>
           <t>09:00~18:00</t>
@@ -11441,43 +11656,53 @@
       </c>
     </row>
     <row r="160">
-      <c r="C160" s="3" t="n">
+      <c r="A160" s="16" t="n"/>
+      <c r="B160" s="16" t="n"/>
+      <c r="C160" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="D160" s="14" t="inlineStr">
         <is>
           <t>월성경로당</t>
         </is>
       </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F160" s="3" t="inlineStr">
+      <c r="E160" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F160" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 월계동 393-13 </t>
         </is>
       </c>
-      <c r="G160" s="3" t="inlineStr">
+      <c r="G160" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 광운로13길 9 (월계동)</t>
         </is>
       </c>
-      <c r="H160" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I160" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J160" s="3" t="n">
+      <c r="H160" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" s="14" t="n">
         <v>96.63</v>
       </c>
-      <c r="M160" s="3" t="inlineStr">
+      <c r="K160" s="16" t="n"/>
+      <c r="L160" s="16" t="n"/>
+      <c r="M160" s="14" t="inlineStr">
         <is>
           <t>22-노유자(노인 및 어린이)시설</t>
         </is>
       </c>
+      <c r="N160" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O160" s="16" t="n"/>
       <c r="P160" s="2" t="n"/>
       <c r="BH160" s="3" t="inlineStr">
         <is>
@@ -11486,43 +11711,53 @@
       </c>
     </row>
     <row r="161">
-      <c r="C161" s="3" t="n">
+      <c r="A161" s="16" t="n"/>
+      <c r="B161" s="16" t="n"/>
+      <c r="C161" s="14" t="n">
         <v>79</v>
       </c>
-      <c r="D161" s="3" t="inlineStr">
+      <c r="D161" s="14" t="inlineStr">
         <is>
           <t>수암경로당</t>
         </is>
       </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="inlineStr">
+      <c r="E161" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F161" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 101-187 </t>
         </is>
       </c>
-      <c r="G161" s="3" t="inlineStr">
+      <c r="G161" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 덕릉로115가길 21 (상계동)</t>
         </is>
       </c>
-      <c r="H161" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I161" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J161" s="3" t="n">
+      <c r="H161" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I161" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" s="14" t="n">
         <v>94.52</v>
       </c>
-      <c r="M161" s="3" t="inlineStr">
+      <c r="K161" s="16" t="n"/>
+      <c r="L161" s="16" t="n"/>
+      <c r="M161" s="14" t="inlineStr">
         <is>
           <t>경로당</t>
         </is>
       </c>
+      <c r="N161" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O161" s="16" t="n"/>
       <c r="P161" s="2" t="n"/>
       <c r="BH161" s="3" t="inlineStr">
         <is>
@@ -11531,47 +11766,57 @@
       </c>
     </row>
     <row r="162">
-      <c r="C162" s="3" t="n">
+      <c r="A162" s="16" t="n"/>
+      <c r="B162" s="16" t="n"/>
+      <c r="C162" s="14" t="n">
         <v>81</v>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="D162" s="14" t="inlineStr">
         <is>
           <t>목공소</t>
         </is>
       </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="inlineStr">
+      <c r="E162" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F162" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 132 목공소 </t>
         </is>
       </c>
-      <c r="G162" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I162" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J162" s="3" t="n">
+      <c r="G162" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H162" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I162" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J162" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="M162" s="3" t="inlineStr">
+      <c r="K162" s="16" t="n"/>
+      <c r="L162" s="16" t="n"/>
+      <c r="M162" s="14" t="inlineStr">
         <is>
           <t>목공예체험장</t>
         </is>
       </c>
+      <c r="N162" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O162" s="16" t="n"/>
       <c r="P162" s="2" t="n"/>
       <c r="BH162" s="3" t="inlineStr">
         <is>
@@ -11649,45 +11894,55 @@
       <c r="BH163" s="3" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="C164" s="3" t="n">
+      <c r="A164" s="16" t="n"/>
+      <c r="B164" s="16" t="n"/>
+      <c r="C164" s="14" t="n">
         <v>59</v>
       </c>
-      <c r="D164" s="3" t="inlineStr">
+      <c r="D164" s="14" t="inlineStr">
         <is>
           <t>이지체험주택</t>
         </is>
       </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
+      <c r="E164" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F164" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 하계동 251-8 </t>
         </is>
       </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="n">
+      <c r="G164" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H164" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J164" s="3" t="n">
+      <c r="I164" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J164" s="14" t="n">
         <v>85.17</v>
       </c>
-      <c r="M164" s="3" t="inlineStr">
+      <c r="K164" s="16" t="n"/>
+      <c r="L164" s="16" t="n"/>
+      <c r="M164" s="14" t="inlineStr">
         <is>
           <t>08-교육연구 및 복지시설</t>
         </is>
       </c>
+      <c r="N164" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O164" s="16" t="n"/>
       <c r="P164" s="2" t="n"/>
       <c r="BH164" s="3" t="inlineStr">
         <is>
@@ -11965,43 +12220,53 @@
       </c>
     </row>
     <row r="170">
-      <c r="C170" s="3" t="n">
+      <c r="A170" s="16" t="n"/>
+      <c r="B170" s="16" t="n"/>
+      <c r="C170" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="D170" s="3" t="inlineStr">
+      <c r="D170" s="14" t="inlineStr">
         <is>
           <t>연촌사랑방</t>
         </is>
       </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="inlineStr">
+      <c r="E170" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F170" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 월계동 392-59 </t>
         </is>
       </c>
-      <c r="G170" s="3" t="inlineStr">
+      <c r="G170" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 광운로17길 48-4 (월계동)</t>
         </is>
       </c>
-      <c r="H170" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I170" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J170" s="3" t="n">
+      <c r="H170" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" s="14" t="n">
         <v>75.93000000000001</v>
       </c>
-      <c r="M170" s="3" t="inlineStr">
+      <c r="K170" s="16" t="n"/>
+      <c r="L170" s="16" t="n"/>
+      <c r="M170" s="14" t="inlineStr">
         <is>
           <t>자연친화적 학습공간</t>
         </is>
       </c>
+      <c r="N170" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O170" s="16" t="n"/>
       <c r="P170" s="2" t="n"/>
       <c r="BH170" s="3" t="inlineStr">
         <is>
@@ -12139,43 +12404,53 @@
       </c>
     </row>
     <row r="173">
-      <c r="C173" s="3" t="n">
+      <c r="A173" s="16" t="n"/>
+      <c r="B173" s="16" t="n"/>
+      <c r="C173" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="D173" s="14" t="inlineStr">
         <is>
           <t>비석골근린공원내공중화장실</t>
         </is>
       </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
+      <c r="E173" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F173" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 월계동 779 비석골근린공원내공중화장실 </t>
         </is>
       </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H173" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I173" s="3" t="n">
+      <c r="G173" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H173" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J173" s="3" t="n">
+      <c r="J173" s="14" t="n">
         <v>69.16</v>
       </c>
-      <c r="M173" s="3" t="inlineStr">
+      <c r="K173" s="16" t="n"/>
+      <c r="L173" s="16" t="n"/>
+      <c r="M173" s="14" t="inlineStr">
         <is>
           <t>19-공공용시설</t>
         </is>
       </c>
+      <c r="N173" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O173" s="16" t="n"/>
       <c r="P173" s="2" t="inlineStr">
         <is>
           <t>06:00~21:50</t>
@@ -12671,47 +12946,57 @@
       </c>
     </row>
     <row r="182">
-      <c r="C182" s="3" t="n">
+      <c r="A182" s="16" t="n"/>
+      <c r="B182" s="16" t="n"/>
+      <c r="C182" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="D182" s="3" t="inlineStr">
+      <c r="D182" s="14" t="inlineStr">
         <is>
           <t>목공예방</t>
         </is>
       </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F182" s="3" t="inlineStr">
+      <c r="E182" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F182" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 공릉동 29-2 </t>
         </is>
       </c>
-      <c r="G182" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I182" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J182" s="3" t="n">
+      <c r="G182" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H182" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I182" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J182" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="M182" s="3" t="inlineStr">
+      <c r="K182" s="16" t="n"/>
+      <c r="L182" s="16" t="n"/>
+      <c r="M182" s="14" t="inlineStr">
         <is>
           <t>주민편의시설(목공예체험장)</t>
         </is>
       </c>
+      <c r="N182" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O182" s="16" t="n"/>
       <c r="P182" s="2" t="n"/>
       <c r="BH182" s="3" t="inlineStr">
         <is>
@@ -13041,47 +13326,57 @@
       </c>
     </row>
     <row r="188">
-      <c r="C188" s="3" t="n">
+      <c r="A188" s="16" t="n"/>
+      <c r="B188" s="16" t="n"/>
+      <c r="C188" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="D188" s="3" t="inlineStr">
+      <c r="D188" s="14" t="inlineStr">
         <is>
           <t>월계1동지역경로당 건물</t>
         </is>
       </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F188" s="3" t="inlineStr">
+      <c r="E188" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F188" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 월계동 500-30 101호 </t>
         </is>
       </c>
-      <c r="G188" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H188" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I188" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J188" s="3" t="n">
+      <c r="G188" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H188" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I188" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J188" s="14" t="n">
         <v>51.8</v>
       </c>
-      <c r="M188" s="3" t="inlineStr">
+      <c r="K188" s="16" t="n"/>
+      <c r="L188" s="16" t="n"/>
+      <c r="M188" s="14" t="inlineStr">
         <is>
           <t>공동주택 경로당</t>
         </is>
       </c>
+      <c r="N188" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O188" s="16" t="n"/>
       <c r="P188" s="2" t="n"/>
       <c r="S188" s="3" t="n">
         <v>162.25</v>
@@ -13093,43 +13388,53 @@
       </c>
     </row>
     <row r="189">
-      <c r="C189" s="3" t="n">
+      <c r="A189" s="16" t="n"/>
+      <c r="B189" s="16" t="n"/>
+      <c r="C189" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="D189" s="3" t="inlineStr">
+      <c r="D189" s="14" t="inlineStr">
         <is>
           <t>공릉경로당</t>
         </is>
       </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="inlineStr">
+      <c r="E189" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F189" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 공릉동 415-36 지하층 비01호</t>
         </is>
       </c>
-      <c r="G189" s="3" t="inlineStr">
+      <c r="G189" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 공릉로 169-7  비01호 (공릉동 지하층)</t>
         </is>
       </c>
-      <c r="H189" s="3" t="n">
+      <c r="H189" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="I189" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J189" s="3" t="n">
+      <c r="I189" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" s="14" t="n">
         <v>49.54</v>
       </c>
-      <c r="M189" s="3" t="inlineStr">
+      <c r="K189" s="16" t="n"/>
+      <c r="L189" s="16" t="n"/>
+      <c r="M189" s="14" t="inlineStr">
         <is>
           <t>경로당</t>
         </is>
       </c>
+      <c r="N189" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O189" s="16" t="n"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
           <t>10:00~19:00</t>
@@ -13263,47 +13568,57 @@
       </c>
     </row>
     <row r="192">
-      <c r="C192" s="3" t="n">
+      <c r="A192" s="16" t="n"/>
+      <c r="B192" s="16" t="n"/>
+      <c r="C192" s="14" t="n">
         <v>156</v>
       </c>
-      <c r="D192" s="3" t="inlineStr">
+      <c r="D192" s="14" t="inlineStr">
         <is>
           <t>상계수락경로당</t>
         </is>
       </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="inlineStr">
+      <c r="E192" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F192" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 1116-64 201호 </t>
         </is>
       </c>
-      <c r="G192" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H192" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I192" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J192" s="3" t="n">
+      <c r="G192" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H192" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I192" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J192" s="14" t="n">
         <v>43.35</v>
       </c>
-      <c r="M192" s="3" t="inlineStr">
+      <c r="K192" s="16" t="n"/>
+      <c r="L192" s="16" t="n"/>
+      <c r="M192" s="14" t="inlineStr">
         <is>
           <t>08-교육연구 및 복지시설</t>
         </is>
       </c>
+      <c r="N192" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O192" s="16" t="n"/>
       <c r="P192" s="2" t="n"/>
       <c r="BH192" s="3" t="inlineStr">
         <is>
@@ -13368,45 +13683,55 @@
       </c>
     </row>
     <row r="194">
-      <c r="C194" s="3" t="n">
+      <c r="A194" s="16" t="n"/>
+      <c r="B194" s="16" t="n"/>
+      <c r="C194" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D194" s="3" t="inlineStr">
+      <c r="D194" s="14" t="inlineStr">
         <is>
           <t>인덕마을경로당</t>
         </is>
       </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
+      <c r="E194" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F194" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 월계동 272-62 1층2호 </t>
         </is>
       </c>
-      <c r="G194" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H194" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I194" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J194" s="3" t="n">
+      <c r="G194" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H194" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J194" s="14" t="n">
         <v>43.21</v>
       </c>
-      <c r="M194" s="3" t="inlineStr">
+      <c r="K194" s="16" t="n"/>
+      <c r="L194" s="16" t="n"/>
+      <c r="M194" s="14" t="inlineStr">
         <is>
           <t>02-공동주택</t>
         </is>
       </c>
+      <c r="N194" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O194" s="16" t="n"/>
       <c r="P194" s="2" t="inlineStr">
         <is>
           <t>09:00~18:00(월~금)/09:00~17:00(토,일)</t>
@@ -13726,45 +14051,55 @@
       </c>
     </row>
     <row r="200">
-      <c r="C200" s="3" t="n">
+      <c r="A200" s="16" t="n"/>
+      <c r="B200" s="16" t="n"/>
+      <c r="C200" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D200" s="14" t="inlineStr">
         <is>
           <t>제33녹지관리초소</t>
         </is>
       </c>
-      <c r="E200" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
+      <c r="E200" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F200" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 공릉동 29-28 </t>
         </is>
       </c>
-      <c r="G200" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H200" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I200" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J200" s="3" t="n">
+      <c r="G200" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H200" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J200" s="14" t="n">
         <v>34.84</v>
       </c>
-      <c r="M200" s="3" t="inlineStr">
+      <c r="K200" s="16" t="n"/>
+      <c r="L200" s="16" t="n"/>
+      <c r="M200" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N200" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O200" s="16" t="n"/>
       <c r="P200" s="2" t="inlineStr">
         <is>
           <t>09:00~18:00</t>
@@ -14018,45 +14353,55 @@
       </c>
     </row>
     <row r="205">
-      <c r="C205" s="3" t="n">
+      <c r="A205" s="16" t="n"/>
+      <c r="B205" s="16" t="n"/>
+      <c r="C205" s="14" t="n">
         <v>167</v>
       </c>
-      <c r="D205" s="3" t="inlineStr">
+      <c r="D205" s="14" t="inlineStr">
         <is>
           <t>수락산5호화장실</t>
         </is>
       </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="inlineStr">
+      <c r="E205" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F205" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 1-2 </t>
         </is>
       </c>
-      <c r="G205" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H205" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I205" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J205" s="3" t="n">
+      <c r="G205" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H205" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J205" s="14" t="n">
         <v>19.74</v>
       </c>
-      <c r="M205" s="3" t="inlineStr">
+      <c r="K205" s="16" t="n"/>
+      <c r="L205" s="16" t="n"/>
+      <c r="M205" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N205" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O205" s="16" t="n"/>
       <c r="P205" s="2" t="inlineStr">
         <is>
           <t>10:00~17:30(화~일)</t>
@@ -14138,45 +14483,55 @@
       </c>
     </row>
     <row r="207">
-      <c r="C207" s="3" t="n">
+      <c r="A207" s="16" t="n"/>
+      <c r="B207" s="16" t="n"/>
+      <c r="C207" s="14" t="n">
         <v>182</v>
       </c>
-      <c r="D207" s="3" t="inlineStr">
+      <c r="D207" s="14" t="inlineStr">
         <is>
           <t>불암산화장실</t>
         </is>
       </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
+      <c r="E207" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F207" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 164-5 </t>
         </is>
       </c>
-      <c r="G207" s="3" t="inlineStr">
+      <c r="G207" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 덕릉로118길 29 (상계동)</t>
         </is>
       </c>
-      <c r="H207" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I207" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J207" s="3" t="n">
+      <c r="H207" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J207" s="14" t="n">
         <v>19.74</v>
       </c>
-      <c r="M207" s="3" t="inlineStr">
+      <c r="K207" s="16" t="n"/>
+      <c r="L207" s="16" t="n"/>
+      <c r="M207" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N207" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O207" s="16" t="n"/>
       <c r="P207" s="2" t="n"/>
       <c r="BH207" s="3" t="inlineStr">
         <is>
@@ -14436,45 +14791,55 @@
       </c>
     </row>
     <row r="212">
-      <c r="C212" s="3" t="n">
+      <c r="A212" s="16" t="n"/>
+      <c r="B212" s="16" t="n"/>
+      <c r="C212" s="14" t="n">
         <v>105</v>
       </c>
-      <c r="D212" s="3" t="inlineStr">
+      <c r="D212" s="14" t="inlineStr">
         <is>
           <t>삼들어린이공원화장실</t>
         </is>
       </c>
-      <c r="E212" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F212" s="3" t="inlineStr">
+      <c r="E212" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F212" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 623 </t>
         </is>
       </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H212" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I212" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J212" s="3" t="n">
+      <c r="G212" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H212" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I212" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J212" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M212" s="3" t="inlineStr">
+      <c r="K212" s="16" t="n"/>
+      <c r="L212" s="16" t="n"/>
+      <c r="M212" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N212" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O212" s="16" t="n"/>
       <c r="P212" s="2" t="n"/>
       <c r="BH212" s="3" t="inlineStr">
         <is>
@@ -14483,45 +14848,55 @@
       </c>
     </row>
     <row r="213">
-      <c r="C213" s="3" t="n">
+      <c r="A213" s="16" t="n"/>
+      <c r="B213" s="16" t="n"/>
+      <c r="C213" s="14" t="n">
         <v>106</v>
       </c>
-      <c r="D213" s="3" t="inlineStr">
+      <c r="D213" s="14" t="inlineStr">
         <is>
           <t>산철쭉어린이공원화장실</t>
         </is>
       </c>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F213" s="3" t="inlineStr">
+      <c r="E213" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F213" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 625 </t>
         </is>
       </c>
-      <c r="G213" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H213" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I213" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J213" s="3" t="n">
+      <c r="G213" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H213" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J213" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M213" s="3" t="inlineStr">
+      <c r="K213" s="16" t="n"/>
+      <c r="L213" s="16" t="n"/>
+      <c r="M213" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N213" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O213" s="16" t="n"/>
       <c r="P213" s="2" t="n"/>
       <c r="BH213" s="3" t="inlineStr">
         <is>
@@ -14586,45 +14961,55 @@
       </c>
     </row>
     <row r="215">
-      <c r="C215" s="3" t="n">
+      <c r="A215" s="16" t="n"/>
+      <c r="B215" s="16" t="n"/>
+      <c r="C215" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="D215" s="3" t="inlineStr">
+      <c r="D215" s="14" t="inlineStr">
         <is>
           <t>햇빛어린이공원화장실</t>
         </is>
       </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F215" s="3" t="inlineStr">
+      <c r="E215" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F215" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 646 </t>
         </is>
       </c>
-      <c r="G215" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H215" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I215" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J215" s="3" t="n">
+      <c r="G215" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H215" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J215" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M215" s="3" t="inlineStr">
+      <c r="K215" s="16" t="n"/>
+      <c r="L215" s="16" t="n"/>
+      <c r="M215" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N215" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O215" s="16" t="n"/>
       <c r="P215" s="2" t="n"/>
       <c r="BH215" s="3" t="inlineStr">
         <is>
@@ -14633,43 +15018,53 @@
       </c>
     </row>
     <row r="216">
-      <c r="C216" s="3" t="n">
+      <c r="A216" s="16" t="n"/>
+      <c r="B216" s="16" t="n"/>
+      <c r="C216" s="14" t="n">
         <v>112</v>
       </c>
-      <c r="D216" s="3" t="inlineStr">
+      <c r="D216" s="14" t="inlineStr">
         <is>
           <t>두루미어린이공원화장실</t>
         </is>
       </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F216" s="3" t="inlineStr">
+      <c r="E216" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F216" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 656-1 </t>
         </is>
       </c>
-      <c r="G216" s="3" t="inlineStr">
+      <c r="G216" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 동일로227길 85 (상계동)</t>
         </is>
       </c>
-      <c r="H216" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I216" s="3" t="n">
+      <c r="H216" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J216" s="3" t="n">
+      <c r="J216" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M216" s="3" t="inlineStr">
+      <c r="K216" s="16" t="n"/>
+      <c r="L216" s="16" t="n"/>
+      <c r="M216" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N216" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O216" s="16" t="n"/>
       <c r="P216" s="2" t="n"/>
       <c r="BH216" s="3" t="inlineStr">
         <is>
@@ -14678,45 +15073,55 @@
       </c>
     </row>
     <row r="217">
-      <c r="C217" s="3" t="n">
+      <c r="A217" s="16" t="n"/>
+      <c r="B217" s="16" t="n"/>
+      <c r="C217" s="14" t="n">
         <v>114</v>
       </c>
-      <c r="D217" s="3" t="inlineStr">
+      <c r="D217" s="14" t="inlineStr">
         <is>
           <t>반듸어린이공원화장실</t>
         </is>
       </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="inlineStr">
+      <c r="E217" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F217" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 665 </t>
         </is>
       </c>
-      <c r="G217" s="3" t="inlineStr">
+      <c r="G217" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 노원로 564 (상계동)</t>
         </is>
       </c>
-      <c r="H217" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I217" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J217" s="3" t="n">
+      <c r="H217" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J217" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M217" s="3" t="inlineStr">
+      <c r="K217" s="16" t="n"/>
+      <c r="L217" s="16" t="n"/>
+      <c r="M217" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N217" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O217" s="16" t="n"/>
       <c r="P217" s="2" t="inlineStr">
         <is>
           <t>09:00~18:00(월~금)/09:00~17:00(토,일)</t>
@@ -14781,45 +15186,55 @@
       </c>
     </row>
     <row r="219">
-      <c r="C219" s="3" t="n">
+      <c r="A219" s="16" t="n"/>
+      <c r="B219" s="16" t="n"/>
+      <c r="C219" s="14" t="n">
         <v>116</v>
       </c>
-      <c r="D219" s="3" t="inlineStr">
+      <c r="D219" s="14" t="inlineStr">
         <is>
           <t>달빛어린이공원화장실</t>
         </is>
       </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F219" s="3" t="inlineStr">
+      <c r="E219" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F219" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 670-1 </t>
         </is>
       </c>
-      <c r="G219" s="3" t="inlineStr">
+      <c r="G219" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 노원로 532 (상계동)</t>
         </is>
       </c>
-      <c r="H219" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I219" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J219" s="3" t="n">
+      <c r="H219" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J219" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M219" s="3" t="inlineStr">
+      <c r="K219" s="16" t="n"/>
+      <c r="L219" s="16" t="n"/>
+      <c r="M219" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N219" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O219" s="16" t="n"/>
       <c r="P219" s="2" t="n"/>
       <c r="BH219" s="3" t="inlineStr">
         <is>
@@ -14828,45 +15243,55 @@
       </c>
     </row>
     <row r="220">
-      <c r="C220" s="3" t="n">
+      <c r="A220" s="16" t="n"/>
+      <c r="B220" s="16" t="n"/>
+      <c r="C220" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="D220" s="3" t="inlineStr">
+      <c r="D220" s="14" t="inlineStr">
         <is>
           <t>꿈나무어린이공원화장실</t>
         </is>
       </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="inlineStr">
+      <c r="E220" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F220" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 679 </t>
         </is>
       </c>
-      <c r="G220" s="3" t="inlineStr">
+      <c r="G220" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 노원로38길 46 (상계동)</t>
         </is>
       </c>
-      <c r="H220" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I220" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J220" s="3" t="n">
+      <c r="H220" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J220" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M220" s="3" t="inlineStr">
+      <c r="K220" s="16" t="n"/>
+      <c r="L220" s="16" t="n"/>
+      <c r="M220" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N220" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O220" s="16" t="n"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
           <t>10:00~17:30</t>
@@ -14884,45 +15309,55 @@
       </c>
     </row>
     <row r="221">
-      <c r="C221" s="3" t="n">
+      <c r="A221" s="16" t="n"/>
+      <c r="B221" s="16" t="n"/>
+      <c r="C221" s="14" t="n">
         <v>124</v>
       </c>
-      <c r="D221" s="3" t="inlineStr">
+      <c r="D221" s="14" t="inlineStr">
         <is>
           <t>온곡어린이공원화장실</t>
         </is>
       </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="inlineStr">
+      <c r="E221" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F221" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 692-1 </t>
         </is>
       </c>
-      <c r="G221" s="3" t="inlineStr">
+      <c r="G221" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 동일로 1456 (상계동)</t>
         </is>
       </c>
-      <c r="H221" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I221" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J221" s="3" t="n">
+      <c r="H221" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J221" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M221" s="3" t="inlineStr">
+      <c r="K221" s="16" t="n"/>
+      <c r="L221" s="16" t="n"/>
+      <c r="M221" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N221" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O221" s="16" t="n"/>
       <c r="P221" s="2" t="n"/>
       <c r="BH221" s="3" t="inlineStr">
         <is>
@@ -14931,45 +15366,55 @@
       </c>
     </row>
     <row r="222">
-      <c r="C222" s="3" t="n">
+      <c r="A222" s="16" t="n"/>
+      <c r="B222" s="16" t="n"/>
+      <c r="C222" s="14" t="n">
         <v>133</v>
       </c>
-      <c r="D222" s="3" t="inlineStr">
+      <c r="D222" s="14" t="inlineStr">
         <is>
           <t>채송화어린이공원화장실</t>
         </is>
       </c>
-      <c r="E222" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F222" s="3" t="inlineStr">
+      <c r="E222" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F222" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 737-1 </t>
         </is>
       </c>
-      <c r="G222" s="3" t="inlineStr">
+      <c r="G222" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 동일로215길 48 (상계동)</t>
         </is>
       </c>
-      <c r="H222" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I222" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J222" s="3" t="n">
+      <c r="H222" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I222" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J222" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M222" s="3" t="inlineStr">
+      <c r="K222" s="16" t="n"/>
+      <c r="L222" s="16" t="n"/>
+      <c r="M222" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N222" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O222" s="16" t="n"/>
       <c r="P222" s="2" t="n"/>
       <c r="BH222" s="3" t="inlineStr">
         <is>
@@ -14978,45 +15423,55 @@
       </c>
     </row>
     <row r="223">
-      <c r="C223" s="3" t="n">
+      <c r="A223" s="16" t="n"/>
+      <c r="B223" s="16" t="n"/>
+      <c r="C223" s="14" t="n">
         <v>134</v>
       </c>
-      <c r="D223" s="3" t="inlineStr">
+      <c r="D223" s="14" t="inlineStr">
         <is>
           <t>기린어린이공원화장실</t>
         </is>
       </c>
-      <c r="E223" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F223" s="3" t="inlineStr">
+      <c r="E223" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F223" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 737-3 </t>
         </is>
       </c>
-      <c r="G223" s="3" t="inlineStr">
+      <c r="G223" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 동일로215길 48 (상계동)</t>
         </is>
       </c>
-      <c r="H223" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I223" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J223" s="3" t="n">
+      <c r="H223" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J223" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="M223" s="3" t="inlineStr">
+      <c r="K223" s="16" t="n"/>
+      <c r="L223" s="16" t="n"/>
+      <c r="M223" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N223" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O223" s="16" t="n"/>
       <c r="P223" s="2" t="n"/>
       <c r="BH223" s="3" t="inlineStr">
         <is>
@@ -15025,45 +15480,55 @@
       </c>
     </row>
     <row r="224">
-      <c r="C224" s="3" t="n">
+      <c r="A224" s="16" t="n"/>
+      <c r="B224" s="16" t="n"/>
+      <c r="C224" s="14" t="n">
         <v>161</v>
       </c>
-      <c r="D224" s="3" t="inlineStr">
+      <c r="D224" s="14" t="inlineStr">
         <is>
           <t>수락산8호매점</t>
         </is>
       </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="inlineStr">
+      <c r="E224" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F224" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 1-2 </t>
         </is>
       </c>
-      <c r="G224" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H224" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I224" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J224" s="3" t="n">
+      <c r="G224" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H224" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J224" s="14" t="n">
         <v>11.07</v>
       </c>
-      <c r="M224" s="3" t="inlineStr">
+      <c r="K224" s="16" t="n"/>
+      <c r="L224" s="16" t="n"/>
+      <c r="M224" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N224" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O224" s="16" t="n"/>
       <c r="P224" s="2" t="inlineStr">
         <is>
           <t>09:00~20:00</t>
@@ -15076,45 +15541,55 @@
       </c>
     </row>
     <row r="225">
-      <c r="C225" s="3" t="n">
+      <c r="A225" s="16" t="n"/>
+      <c r="B225" s="16" t="n"/>
+      <c r="C225" s="14" t="n">
         <v>162</v>
       </c>
-      <c r="D225" s="3" t="inlineStr">
+      <c r="D225" s="14" t="inlineStr">
         <is>
           <t>수락산4호매점</t>
         </is>
       </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
+      <c r="E225" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F225" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 1-2 </t>
         </is>
       </c>
-      <c r="G225" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H225" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I225" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J225" s="3" t="n">
+      <c r="G225" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H225" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I225" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J225" s="14" t="n">
         <v>11.07</v>
       </c>
-      <c r="M225" s="3" t="inlineStr">
+      <c r="K225" s="16" t="n"/>
+      <c r="L225" s="16" t="n"/>
+      <c r="M225" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N225" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O225" s="16" t="n"/>
       <c r="P225" s="2" t="n"/>
       <c r="BH225" s="3" t="inlineStr">
         <is>
@@ -15123,45 +15598,55 @@
       </c>
     </row>
     <row r="226">
-      <c r="C226" s="3" t="n">
+      <c r="A226" s="16" t="n"/>
+      <c r="B226" s="16" t="n"/>
+      <c r="C226" s="14" t="n">
         <v>163</v>
       </c>
-      <c r="D226" s="3" t="inlineStr">
+      <c r="D226" s="14" t="inlineStr">
         <is>
           <t>수락산3호매점</t>
         </is>
       </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F226" s="3" t="inlineStr">
+      <c r="E226" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F226" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 1-2 </t>
         </is>
       </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H226" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I226" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J226" s="3" t="n">
+      <c r="G226" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H226" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J226" s="14" t="n">
         <v>11.07</v>
       </c>
-      <c r="M226" s="3" t="inlineStr">
+      <c r="K226" s="16" t="n"/>
+      <c r="L226" s="16" t="n"/>
+      <c r="M226" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N226" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O226" s="16" t="n"/>
       <c r="P226" s="2" t="n"/>
       <c r="BH226" s="3" t="inlineStr">
         <is>
@@ -15170,45 +15655,55 @@
       </c>
     </row>
     <row r="227">
-      <c r="C227" s="3" t="n">
+      <c r="A227" s="16" t="n"/>
+      <c r="B227" s="16" t="n"/>
+      <c r="C227" s="14" t="n">
         <v>164</v>
       </c>
-      <c r="D227" s="3" t="inlineStr">
+      <c r="D227" s="14" t="inlineStr">
         <is>
           <t>수락산2호매점</t>
         </is>
       </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="inlineStr">
+      <c r="E227" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F227" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 1-2 </t>
         </is>
       </c>
-      <c r="G227" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H227" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I227" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J227" s="3" t="n">
+      <c r="G227" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H227" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J227" s="14" t="n">
         <v>11.07</v>
       </c>
-      <c r="M227" s="3" t="inlineStr">
+      <c r="K227" s="16" t="n"/>
+      <c r="L227" s="16" t="n"/>
+      <c r="M227" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N227" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O227" s="16" t="n"/>
       <c r="P227" s="2" t="inlineStr">
         <is>
           <t>09:00~22:00(월~금)/09:00~18:00(토)</t>
@@ -15221,45 +15716,55 @@
       </c>
     </row>
     <row r="228">
-      <c r="C228" s="3" t="n">
+      <c r="A228" s="16" t="n"/>
+      <c r="B228" s="16" t="n"/>
+      <c r="C228" s="14" t="n">
         <v>165</v>
       </c>
-      <c r="D228" s="3" t="inlineStr">
+      <c r="D228" s="14" t="inlineStr">
         <is>
           <t>수락산6호매점</t>
         </is>
       </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="inlineStr">
+      <c r="E228" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F228" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 1-2 </t>
         </is>
       </c>
-      <c r="G228" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H228" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I228" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J228" s="3" t="n">
+      <c r="G228" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H228" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J228" s="14" t="n">
         <v>11.07</v>
       </c>
-      <c r="M228" s="3" t="inlineStr">
+      <c r="K228" s="16" t="n"/>
+      <c r="L228" s="16" t="n"/>
+      <c r="M228" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N228" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O228" s="16" t="n"/>
       <c r="P228" s="2" t="n"/>
       <c r="BH228" s="3" t="inlineStr">
         <is>
@@ -15268,45 +15773,55 @@
       </c>
     </row>
     <row r="229">
-      <c r="C229" s="3" t="n">
+      <c r="A229" s="16" t="n"/>
+      <c r="B229" s="16" t="n"/>
+      <c r="C229" s="14" t="n">
         <v>166</v>
       </c>
-      <c r="D229" s="3" t="inlineStr">
+      <c r="D229" s="14" t="inlineStr">
         <is>
           <t>수락산1호매점</t>
         </is>
       </c>
-      <c r="E229" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F229" s="3" t="inlineStr">
+      <c r="E229" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F229" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 1-2 </t>
         </is>
       </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H229" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I229" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J229" s="3" t="n">
+      <c r="G229" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H229" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J229" s="14" t="n">
         <v>11.07</v>
       </c>
-      <c r="M229" s="3" t="inlineStr">
+      <c r="K229" s="16" t="n"/>
+      <c r="L229" s="16" t="n"/>
+      <c r="M229" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N229" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O229" s="16" t="n"/>
       <c r="P229" s="2" t="n"/>
       <c r="BH229" s="3" t="inlineStr">
         <is>
@@ -15315,45 +15830,55 @@
       </c>
     </row>
     <row r="230">
-      <c r="C230" s="3" t="n">
+      <c r="A230" s="16" t="n"/>
+      <c r="B230" s="16" t="n"/>
+      <c r="C230" s="14" t="n">
         <v>168</v>
       </c>
-      <c r="D230" s="3" t="inlineStr">
+      <c r="D230" s="14" t="inlineStr">
         <is>
           <t>수락산7호매점</t>
         </is>
       </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F230" s="3" t="inlineStr">
+      <c r="E230" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F230" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 1-2 </t>
         </is>
       </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H230" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I230" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J230" s="3" t="n">
+      <c r="G230" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H230" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J230" s="14" t="n">
         <v>11.07</v>
       </c>
-      <c r="M230" s="3" t="inlineStr">
+      <c r="K230" s="16" t="n"/>
+      <c r="L230" s="16" t="n"/>
+      <c r="M230" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N230" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O230" s="16" t="n"/>
       <c r="P230" s="2" t="n"/>
       <c r="BH230" s="3" t="inlineStr">
         <is>
@@ -15362,45 +15887,55 @@
       </c>
     </row>
     <row r="231">
-      <c r="C231" s="3" t="n">
+      <c r="A231" s="16" t="n"/>
+      <c r="B231" s="16" t="n"/>
+      <c r="C231" s="14" t="n">
         <v>169</v>
       </c>
-      <c r="D231" s="3" t="inlineStr">
+      <c r="D231" s="14" t="inlineStr">
         <is>
           <t>수락산5호매점</t>
         </is>
       </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F231" s="3" t="inlineStr">
+      <c r="E231" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F231" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 상계동 산 1-2 </t>
         </is>
       </c>
-      <c r="G231" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H231" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I231" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J231" s="3" t="n">
+      <c r="G231" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H231" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J231" s="14" t="n">
         <v>11.07</v>
       </c>
-      <c r="M231" s="3" t="inlineStr">
+      <c r="K231" s="16" t="n"/>
+      <c r="L231" s="16" t="n"/>
+      <c r="M231" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N231" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O231" s="16" t="n"/>
       <c r="P231" s="2" t="inlineStr">
         <is>
           <t>10:00~16:00</t>
@@ -15653,45 +16188,55 @@
       </c>
     </row>
     <row r="236">
-      <c r="C236" s="3" t="n">
+      <c r="A236" s="16" t="n"/>
+      <c r="B236" s="16" t="n"/>
+      <c r="C236" s="14" t="n">
         <v>63</v>
       </c>
-      <c r="D236" s="3" t="inlineStr">
+      <c r="D236" s="14" t="inlineStr">
         <is>
           <t>중평어린이공원화장실</t>
         </is>
       </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>02-공공용재산</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
+      <c r="E236" s="14" t="inlineStr">
+        <is>
+          <t>02-공공용재산</t>
+        </is>
+      </c>
+      <c r="F236" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">서울특별시 노원구 하계동 271-1 </t>
         </is>
       </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H236" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I236" s="3" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J236" s="3" t="n">
+      <c r="G236" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H236" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" s="14" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J236" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="M236" s="3" t="inlineStr">
+      <c r="K236" s="16" t="n"/>
+      <c r="L236" s="16" t="n"/>
+      <c r="M236" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="N236" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O236" s="16" t="n"/>
       <c r="P236" s="2" t="n"/>
       <c r="BH236" s="3" t="inlineStr">
         <is>
@@ -15752,19 +16297,35 @@
       </c>
     </row>
     <row r="238">
-      <c r="C238" s="3" t="n">
+      <c r="A238" s="16" t="n"/>
+      <c r="B238" s="16" t="n"/>
+      <c r="C238" s="14" t="n">
         <v>238</v>
       </c>
-      <c r="D238" s="3" t="inlineStr">
+      <c r="D238" s="14" t="inlineStr">
         <is>
           <t>당현지구대</t>
         </is>
       </c>
-      <c r="G238" s="3" t="inlineStr">
+      <c r="E238" s="16" t="n"/>
+      <c r="F238" s="16" t="n"/>
+      <c r="G238" s="14" t="inlineStr">
         <is>
           <t>서울특별시 노원구 노원로17길 64</t>
         </is>
       </c>
+      <c r="H238" s="16" t="n"/>
+      <c r="I238" s="16" t="n"/>
+      <c r="J238" s="16" t="n"/>
+      <c r="K238" s="16" t="n"/>
+      <c r="L238" s="16" t="n"/>
+      <c r="M238" s="16" t="n"/>
+      <c r="N238" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O238" s="16" t="n"/>
       <c r="P238" s="2" t="n"/>
       <c r="BH238" s="3" t="inlineStr">
         <is>
@@ -15773,14 +16334,31 @@
       </c>
     </row>
     <row r="239">
-      <c r="C239" s="3" t="n">
+      <c r="A239" s="16" t="n"/>
+      <c r="B239" s="16" t="n"/>
+      <c r="C239" s="14" t="n">
         <v>239</v>
       </c>
-      <c r="D239" s="3" t="inlineStr">
+      <c r="D239" s="14" t="inlineStr">
         <is>
           <t>월계지구대</t>
         </is>
       </c>
+      <c r="E239" s="16" t="n"/>
+      <c r="F239" s="16" t="n"/>
+      <c r="G239" s="16" t="n"/>
+      <c r="H239" s="16" t="n"/>
+      <c r="I239" s="16" t="n"/>
+      <c r="J239" s="16" t="n"/>
+      <c r="K239" s="16" t="n"/>
+      <c r="L239" s="16" t="n"/>
+      <c r="M239" s="16" t="n"/>
+      <c r="N239" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O239" s="16" t="n"/>
       <c r="P239" s="2" t="n"/>
       <c r="BH239" s="3" t="inlineStr">
         <is>
@@ -15789,14 +16367,31 @@
       </c>
     </row>
     <row r="240">
-      <c r="C240" s="3" t="n">
+      <c r="A240" s="16" t="n"/>
+      <c r="B240" s="16" t="n"/>
+      <c r="C240" s="14" t="n">
         <v>240</v>
       </c>
-      <c r="D240" s="3" t="inlineStr">
+      <c r="D240" s="14" t="inlineStr">
         <is>
           <t>화랑지구대</t>
         </is>
       </c>
+      <c r="E240" s="16" t="n"/>
+      <c r="F240" s="16" t="n"/>
+      <c r="G240" s="16" t="n"/>
+      <c r="H240" s="16" t="n"/>
+      <c r="I240" s="16" t="n"/>
+      <c r="J240" s="16" t="n"/>
+      <c r="K240" s="16" t="n"/>
+      <c r="L240" s="16" t="n"/>
+      <c r="M240" s="16" t="n"/>
+      <c r="N240" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O240" s="16" t="n"/>
       <c r="P240" s="2" t="n"/>
       <c r="BH240" s="3" t="inlineStr">
         <is>
@@ -15805,14 +16400,31 @@
       </c>
     </row>
     <row r="241">
-      <c r="C241" s="3" t="n">
+      <c r="A241" s="16" t="n"/>
+      <c r="B241" s="16" t="n"/>
+      <c r="C241" s="14" t="n">
         <v>241</v>
       </c>
-      <c r="D241" s="3" t="inlineStr">
+      <c r="D241" s="14" t="inlineStr">
         <is>
           <t>노원역지구대</t>
         </is>
       </c>
+      <c r="E241" s="16" t="n"/>
+      <c r="F241" s="16" t="n"/>
+      <c r="G241" s="16" t="n"/>
+      <c r="H241" s="16" t="n"/>
+      <c r="I241" s="16" t="n"/>
+      <c r="J241" s="16" t="n"/>
+      <c r="K241" s="16" t="n"/>
+      <c r="L241" s="16" t="n"/>
+      <c r="M241" s="16" t="n"/>
+      <c r="N241" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O241" s="16" t="n"/>
       <c r="P241" s="2" t="n"/>
       <c r="BH241" s="3" t="inlineStr">
         <is>
@@ -15821,14 +16433,31 @@
       </c>
     </row>
     <row r="242">
-      <c r="C242" s="3" t="n">
+      <c r="A242" s="16" t="n"/>
+      <c r="B242" s="16" t="n"/>
+      <c r="C242" s="14" t="n">
         <v>242</v>
       </c>
-      <c r="D242" s="3" t="inlineStr">
+      <c r="D242" s="14" t="inlineStr">
         <is>
           <t>불암지구대</t>
         </is>
       </c>
+      <c r="E242" s="16" t="n"/>
+      <c r="F242" s="16" t="n"/>
+      <c r="G242" s="16" t="n"/>
+      <c r="H242" s="16" t="n"/>
+      <c r="I242" s="16" t="n"/>
+      <c r="J242" s="16" t="n"/>
+      <c r="K242" s="16" t="n"/>
+      <c r="L242" s="16" t="n"/>
+      <c r="M242" s="16" t="n"/>
+      <c r="N242" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O242" s="16" t="n"/>
       <c r="P242" s="2" t="n"/>
       <c r="BH242" s="3" t="inlineStr">
         <is>
@@ -15837,14 +16466,31 @@
       </c>
     </row>
     <row r="243">
-      <c r="C243" s="3" t="n">
+      <c r="A243" s="16" t="n"/>
+      <c r="B243" s="16" t="n"/>
+      <c r="C243" s="14" t="n">
         <v>243</v>
       </c>
-      <c r="D243" s="3" t="inlineStr">
+      <c r="D243" s="14" t="inlineStr">
         <is>
           <t>마들지구대</t>
         </is>
       </c>
+      <c r="E243" s="16" t="n"/>
+      <c r="F243" s="16" t="n"/>
+      <c r="G243" s="16" t="n"/>
+      <c r="H243" s="16" t="n"/>
+      <c r="I243" s="16" t="n"/>
+      <c r="J243" s="16" t="n"/>
+      <c r="K243" s="16" t="n"/>
+      <c r="L243" s="16" t="n"/>
+      <c r="M243" s="16" t="n"/>
+      <c r="N243" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O243" s="16" t="n"/>
       <c r="P243" s="2" t="n"/>
       <c r="BH243" s="3" t="inlineStr">
         <is>
@@ -15853,14 +16499,31 @@
       </c>
     </row>
     <row r="244">
-      <c r="C244" s="3" t="n">
+      <c r="A244" s="16" t="n"/>
+      <c r="B244" s="16" t="n"/>
+      <c r="C244" s="14" t="n">
         <v>244</v>
       </c>
-      <c r="D244" s="3" t="inlineStr">
+      <c r="D244" s="14" t="inlineStr">
         <is>
           <t>당고개파출소</t>
         </is>
       </c>
+      <c r="E244" s="16" t="n"/>
+      <c r="F244" s="16" t="n"/>
+      <c r="G244" s="16" t="n"/>
+      <c r="H244" s="16" t="n"/>
+      <c r="I244" s="16" t="n"/>
+      <c r="J244" s="16" t="n"/>
+      <c r="K244" s="16" t="n"/>
+      <c r="L244" s="16" t="n"/>
+      <c r="M244" s="16" t="n"/>
+      <c r="N244" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O244" s="16" t="n"/>
       <c r="P244" s="2" t="n"/>
       <c r="BH244" s="3" t="inlineStr">
         <is>
@@ -15869,14 +16532,31 @@
       </c>
     </row>
     <row r="245">
-      <c r="C245" s="3" t="n">
+      <c r="A245" s="16" t="n"/>
+      <c r="B245" s="16" t="n"/>
+      <c r="C245" s="14" t="n">
         <v>245</v>
       </c>
-      <c r="D245" s="3" t="inlineStr">
+      <c r="D245" s="14" t="inlineStr">
         <is>
           <t>상계1파출소</t>
         </is>
       </c>
+      <c r="E245" s="16" t="n"/>
+      <c r="F245" s="16" t="n"/>
+      <c r="G245" s="16" t="n"/>
+      <c r="H245" s="16" t="n"/>
+      <c r="I245" s="16" t="n"/>
+      <c r="J245" s="16" t="n"/>
+      <c r="K245" s="16" t="n"/>
+      <c r="L245" s="16" t="n"/>
+      <c r="M245" s="16" t="n"/>
+      <c r="N245" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O245" s="16" t="n"/>
       <c r="P245" s="2" t="n"/>
       <c r="BH245" s="3" t="inlineStr">
         <is>
@@ -15885,14 +16565,31 @@
       </c>
     </row>
     <row r="246">
-      <c r="C246" s="3" t="n">
+      <c r="A246" s="16" t="n"/>
+      <c r="B246" s="16" t="n"/>
+      <c r="C246" s="14" t="n">
         <v>246</v>
       </c>
-      <c r="D246" s="3" t="inlineStr">
+      <c r="D246" s="14" t="inlineStr">
         <is>
           <t>노원소방서</t>
         </is>
       </c>
+      <c r="E246" s="16" t="n"/>
+      <c r="F246" s="16" t="n"/>
+      <c r="G246" s="16" t="n"/>
+      <c r="H246" s="16" t="n"/>
+      <c r="I246" s="16" t="n"/>
+      <c r="J246" s="16" t="n"/>
+      <c r="K246" s="16" t="n"/>
+      <c r="L246" s="16" t="n"/>
+      <c r="M246" s="16" t="n"/>
+      <c r="N246" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O246" s="16" t="n"/>
       <c r="P246" s="2" t="n"/>
       <c r="BH246" s="3" t="inlineStr">
         <is>
@@ -15958,14 +16655,31 @@
       <c r="BH247" s="3" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="C248" s="3" t="n">
+      <c r="A248" s="16" t="n"/>
+      <c r="B248" s="16" t="n"/>
+      <c r="C248" s="14" t="n">
         <v>249</v>
       </c>
-      <c r="D248" s="3" t="inlineStr">
+      <c r="D248" s="14" t="inlineStr">
         <is>
           <t>월계119안전센터</t>
         </is>
       </c>
+      <c r="E248" s="16" t="n"/>
+      <c r="F248" s="16" t="n"/>
+      <c r="G248" s="16" t="n"/>
+      <c r="H248" s="16" t="n"/>
+      <c r="I248" s="16" t="n"/>
+      <c r="J248" s="16" t="n"/>
+      <c r="K248" s="16" t="n"/>
+      <c r="L248" s="16" t="n"/>
+      <c r="M248" s="16" t="n"/>
+      <c r="N248" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O248" s="16" t="n"/>
       <c r="P248" s="2" t="n"/>
       <c r="BH248" s="3" t="inlineStr">
         <is>
@@ -15974,14 +16688,31 @@
       </c>
     </row>
     <row r="249">
-      <c r="C249" s="3" t="n">
+      <c r="A249" s="16" t="n"/>
+      <c r="B249" s="16" t="n"/>
+      <c r="C249" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="D249" s="3" t="inlineStr">
+      <c r="D249" s="14" t="inlineStr">
         <is>
           <t>수락119안전센터</t>
         </is>
       </c>
+      <c r="E249" s="16" t="n"/>
+      <c r="F249" s="16" t="n"/>
+      <c r="G249" s="16" t="n"/>
+      <c r="H249" s="16" t="n"/>
+      <c r="I249" s="16" t="n"/>
+      <c r="J249" s="16" t="n"/>
+      <c r="K249" s="16" t="n"/>
+      <c r="L249" s="16" t="n"/>
+      <c r="M249" s="16" t="n"/>
+      <c r="N249" s="17" t="inlineStr">
+        <is>
+          <t>✕ 매칭 안됨</t>
+        </is>
+      </c>
+      <c r="O249" s="16" t="n"/>
       <c r="P249" s="2" t="n"/>
       <c r="BH249" s="3" t="inlineStr">
         <is>
